--- a/InputData/trans/BSfVBP/BAU Subsidy for Vehicle Battery Production.xlsx
+++ b/InputData/trans/BSfVBP/BAU Subsidy for Vehicle Battery Production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreazafra/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\trans\BSfVBP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AE0238-5B1A-DA42-881B-ED34965DDF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82747F76-852C-43B8-9E2A-44F7597E129D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34200" yWindow="4040" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -419,17 +419,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="101.33203125" customWidth="1"/>
+    <col min="2" max="2" width="101.31640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -437,12 +437,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -457,10 +457,10 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -554,8 +554,68 @@
       <c r="AE1">
         <v>2050</v>
       </c>
+      <c r="AF1">
+        <v>2051</v>
+      </c>
+      <c r="AG1">
+        <v>2052</v>
+      </c>
+      <c r="AH1">
+        <v>2053</v>
+      </c>
+      <c r="AI1">
+        <v>2054</v>
+      </c>
+      <c r="AJ1">
+        <v>2055</v>
+      </c>
+      <c r="AK1">
+        <v>2056</v>
+      </c>
+      <c r="AL1">
+        <v>2057</v>
+      </c>
+      <c r="AM1">
+        <v>2058</v>
+      </c>
+      <c r="AN1">
+        <v>2059</v>
+      </c>
+      <c r="AO1">
+        <v>2060</v>
+      </c>
+      <c r="AP1">
+        <v>2061</v>
+      </c>
+      <c r="AQ1">
+        <v>2062</v>
+      </c>
+      <c r="AR1">
+        <v>2063</v>
+      </c>
+      <c r="AS1">
+        <v>2064</v>
+      </c>
+      <c r="AT1">
+        <v>2065</v>
+      </c>
+      <c r="AU1">
+        <v>2066</v>
+      </c>
+      <c r="AV1">
+        <v>2067</v>
+      </c>
+      <c r="AW1">
+        <v>2068</v>
+      </c>
+      <c r="AX1">
+        <v>2069</v>
+      </c>
+      <c r="AY1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -657,6 +717,66 @@
         <v>0</v>
       </c>
       <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
         <v>0</v>
       </c>
     </row>
@@ -666,6 +786,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -809,22 +944,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED5FC8E9-13FC-454C-8096-E9609F8E3A5E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A693093-C212-4C3D-9713-B57B2BCEFE67}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D14EF37-986B-4EC4-BE9F-05AF76AEC228}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -840,21 +977,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A693093-C212-4C3D-9713-B57B2BCEFE67}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED5FC8E9-13FC-454C-8096-E9609F8E3A5E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>